--- a/补丁导入.xlsx
+++ b/补丁导入.xlsx
@@ -435,64 +435,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="12"/>
-    <col customWidth="1" max="2" min="2" width="60"/>
-    <col customWidth="1" max="3" min="3" width="10"/>
+    <col customWidth="1" max="2" min="2" width="12"/>
+    <col customWidth="1" max="3" min="3" width="12"/>
     <col customWidth="1" max="4" min="4" width="12"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
+    <col customWidth="1" max="5" min="5" width="60"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>补丁类型</t>
+          <t>补丁日期</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>任务名称/标题</t>
+          <t>Bug编号</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>产品</t>
+          <t>需求编号</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>版本</t>
+          <t>补丁范围</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>补丁日期</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>提示：补丁类型填写 Bug修复 或 紧急需求</t>
+          <t>描述</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bug修复</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>【示例】Bug标题示例</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>ERP</t>
-        </is>
-      </c>
+          <t>39408</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>8.37版本</t>
@@ -500,71 +491,76 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>版本格式：如 8.37版本</t>
+          <t>【君乐宝】【123baby】君乐宝老客下单联合新客，校验通过了（应该提示老客不允许参加活动）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>紧急需求</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>【示例】紧急需求示例</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>POS</t>
-        </is>
-      </c>
+          <t>39381</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>9.16版本</t>
+          <t>8.35版本</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>日期格式：YYYY-MM-DD</t>
+          <t>【6400】沃伦母婴盘点负库存问题</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Bug修复</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>【示例】另一个Bug示例</t>
-        </is>
-      </c>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SCRM</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1.52版本</t>
+          <t>8.37版本</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>【定制】【君乐宝】线上联合新客活动</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>39369</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8.37版本</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>【格瑞丽家】门店POS双屏视频及图片不显示</t>
         </is>
       </c>
     </row>

--- a/补丁导入.xlsx
+++ b/补丁导入.xlsx
@@ -440,7 +440,7 @@
   <cols>
     <col customWidth="1" max="1" min="1" width="12"/>
     <col customWidth="1" max="2" min="2" width="12"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
+    <col customWidth="1" max="3" min="3" width="14"/>
     <col customWidth="1" max="4" min="4" width="12"/>
     <col customWidth="1" max="5" min="5" width="60"/>
   </cols>
@@ -453,12 +453,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Bug编号</t>
+          <t>补丁类型</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>需求编号</t>
+          <t>Bug/需求编号</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -480,10 +480,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>39408</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>8.37版本</t>
@@ -503,10 +507,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>39381</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>8.35版本</t>
@@ -524,7 +532,11 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>紧急需求</t>
+        </is>
+      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>6884</t>
@@ -549,10 +561,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Bug修复</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>39369</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>8.37版本</t>

--- a/补丁导入.xlsx
+++ b/补丁导入.xlsx
@@ -441,8 +441,8 @@
     <col customWidth="1" max="1" min="1" width="12"/>
     <col customWidth="1" max="2" min="2" width="12"/>
     <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="12"/>
-    <col customWidth="1" max="5" min="5" width="60"/>
+    <col customWidth="1" max="4" min="4" width="60"/>
+    <col customWidth="1" max="5" min="5" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>补丁范围</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>描述</t>
         </is>
       </c>
     </row>
@@ -490,12 +490,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>【君乐宝】【123baby】君乐宝老客下单联合新客，校验通过了（应该提示老客不允许参加活动）</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>8.37版本</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>【君乐宝】【123baby】君乐宝老客下单联合新客，校验通过了（应该提示老客不允许参加活动）</t>
         </is>
       </c>
     </row>
@@ -517,12 +517,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>【6400】沃伦母婴盘点负库存问题</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>8.35版本</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>【6400】沃伦母婴盘点负库存问题</t>
         </is>
       </c>
     </row>
@@ -544,12 +544,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>【定制】【君乐宝】线上联合新客活动</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>8.37版本</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>【定制】【君乐宝】线上联合新客活动</t>
         </is>
       </c>
     </row>
@@ -571,12 +571,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>【格瑞丽家】门店POS双屏视频及图片不显示</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>8.37版本</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>【格瑞丽家】门店POS双屏视频及图片不显示</t>
         </is>
       </c>
     </row>
